--- a/artfynd/A 21846-2024 artfynd.xlsx
+++ b/artfynd/A 21846-2024 artfynd.xlsx
@@ -928,7 +928,7 @@
         <v>53065866</v>
       </c>
       <c r="B4" t="n">
-        <v>56395</v>
+        <v>57478</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -969,10 +969,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>616419.7890638429</v>
+        <v>616420</v>
       </c>
       <c r="R4" t="n">
-        <v>6960640.008963236</v>
+        <v>6960640</v>
       </c>
       <c r="S4" t="n">
         <v>100</v>
@@ -1002,19 +1002,9 @@
           <t>2012-09-26</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2012-09-26</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">

--- a/artfynd/A 21846-2024 artfynd.xlsx
+++ b/artfynd/A 21846-2024 artfynd.xlsx
@@ -928,7 +928,7 @@
         <v>53065866</v>
       </c>
       <c r="B4" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 21846-2024 artfynd.xlsx
+++ b/artfynd/A 21846-2024 artfynd.xlsx
@@ -928,7 +928,7 @@
         <v>53065866</v>
       </c>
       <c r="B4" t="n">
-        <v>57481</v>
+        <v>57487</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 21846-2024 artfynd.xlsx
+++ b/artfynd/A 21846-2024 artfynd.xlsx
@@ -928,7 +928,7 @@
         <v>53065866</v>
       </c>
       <c r="B4" t="n">
-        <v>57487</v>
+        <v>57490</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
